--- a/pension_data_export.xlsx
+++ b/pension_data_export.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gdcan\OneDrive\Desktop\Code\Github\civil-war-pension-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A298C7-F81C-43CC-A500-BA41CC7F5717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CE575C-ECE8-4FE5-8F3C-3A98127FA1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19735,7 +19735,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T670"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
@@ -19758,7 +19758,7 @@
     <col min="20" max="20" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19820,7 +19820,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>10</v>
       </c>
@@ -19879,7 +19879,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>11</v>
       </c>
@@ -19938,7 +19938,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>12</v>
       </c>
@@ -19997,7 +19997,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>14</v>
       </c>
@@ -20056,7 +20056,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>16</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>20</v>
       </c>
@@ -20174,7 +20174,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>22</v>
       </c>
@@ -20233,7 +20233,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>24</v>
       </c>
@@ -20286,7 +20286,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26</v>
       </c>
@@ -20339,7 +20339,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>28</v>
       </c>
@@ -20398,7 +20398,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>30</v>
       </c>
@@ -20457,7 +20457,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>32</v>
       </c>
@@ -20516,7 +20516,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>34</v>
       </c>
@@ -20575,7 +20575,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>36</v>
       </c>
@@ -20634,7 +20634,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>38</v>
       </c>
@@ -20687,7 +20687,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>40</v>
       </c>
@@ -20746,7 +20746,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>42</v>
       </c>
@@ -20799,7 +20799,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>44</v>
       </c>
@@ -20852,7 +20852,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>46</v>
       </c>
@@ -20911,7 +20911,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>48</v>
       </c>
@@ -20964,7 +20964,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>50</v>
       </c>
@@ -21023,7 +21023,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>52</v>
       </c>
@@ -21076,7 +21076,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>54</v>
       </c>
@@ -21135,7 +21135,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>56</v>
       </c>
@@ -21188,7 +21188,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>58</v>
       </c>
@@ -21241,7 +21241,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>59</v>
       </c>
@@ -21294,7 +21294,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>61</v>
       </c>
@@ -21347,7 +21347,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>63</v>
       </c>
@@ -21400,7 +21400,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>64</v>
       </c>
@@ -21459,7 +21459,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>97</v>
       </c>
@@ -21518,7 +21518,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>117</v>
       </c>
@@ -21571,7 +21571,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>118</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>119</v>
       </c>
@@ -21689,7 +21689,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>596</v>
       </c>
@@ -21742,7 +21742,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>597</v>
       </c>
@@ -21801,7 +21801,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>598</v>
       </c>
@@ -21854,7 +21854,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>599</v>
       </c>
@@ -21913,7 +21913,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>600</v>
       </c>
@@ -21972,7 +21972,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>601</v>
       </c>
@@ -22031,7 +22031,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>602</v>
       </c>
@@ -22090,7 +22090,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>603</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>604</v>
       </c>
@@ -22202,7 +22202,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>605</v>
       </c>
@@ -22255,7 +22255,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>606</v>
       </c>
@@ -22314,7 +22314,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>607</v>
       </c>
@@ -22367,7 +22367,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>608</v>
       </c>
@@ -22426,7 +22426,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>609</v>
       </c>
@@ -22479,7 +22479,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>624</v>
       </c>
@@ -22538,7 +22538,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>625</v>
       </c>
@@ -22597,7 +22597,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>626</v>
       </c>
@@ -22656,7 +22656,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>627</v>
       </c>
@@ -22715,7 +22715,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>628</v>
       </c>
@@ -22774,7 +22774,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>629</v>
       </c>
@@ -22833,7 +22833,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>630</v>
       </c>
@@ -22886,7 +22886,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>631</v>
       </c>
@@ -22945,7 +22945,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>632</v>
       </c>
@@ -23004,7 +23004,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>633</v>
       </c>
@@ -23063,7 +23063,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>634</v>
       </c>
@@ -23122,7 +23122,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>635</v>
       </c>
@@ -23181,7 +23181,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>636</v>
       </c>
@@ -23240,7 +23240,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>637</v>
       </c>
@@ -23299,7 +23299,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>638</v>
       </c>
@@ -23358,7 +23358,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>674</v>
       </c>
@@ -23417,7 +23417,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>675</v>
       </c>
@@ -23476,7 +23476,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>676</v>
       </c>
@@ -23535,7 +23535,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>677</v>
       </c>
@@ -23594,7 +23594,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>678</v>
       </c>
@@ -23653,7 +23653,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>679</v>
       </c>
@@ -23712,7 +23712,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>680</v>
       </c>
@@ -23771,7 +23771,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>681</v>
       </c>
@@ -23830,7 +23830,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>682</v>
       </c>
@@ -23889,7 +23889,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>683</v>
       </c>
@@ -23948,7 +23948,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>684</v>
       </c>
@@ -24007,7 +24007,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>685</v>
       </c>
@@ -24066,7 +24066,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>686</v>
       </c>
@@ -24125,7 +24125,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>687</v>
       </c>
@@ -24184,7 +24184,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>688</v>
       </c>
@@ -24243,7 +24243,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>716</v>
       </c>
@@ -24302,7 +24302,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>717</v>
       </c>
@@ -24361,7 +24361,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>718</v>
       </c>
@@ -24420,7 +24420,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>719</v>
       </c>
@@ -24479,7 +24479,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>720</v>
       </c>
@@ -24538,7 +24538,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>721</v>
       </c>
@@ -24597,7 +24597,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>722</v>
       </c>
@@ -24656,7 +24656,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>723</v>
       </c>
@@ -24715,7 +24715,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>724</v>
       </c>
@@ -24774,7 +24774,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>725</v>
       </c>
@@ -24833,7 +24833,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>726</v>
       </c>
@@ -24892,7 +24892,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>727</v>
       </c>
@@ -24951,7 +24951,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>728</v>
       </c>
@@ -25010,7 +25010,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>729</v>
       </c>
@@ -25069,7 +25069,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>750</v>
       </c>
@@ -25128,7 +25128,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>751</v>
       </c>
@@ -25187,7 +25187,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>752</v>
       </c>
@@ -25246,7 +25246,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>753</v>
       </c>
@@ -25305,7 +25305,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>754</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>755</v>
       </c>
@@ -25423,7 +25423,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>756</v>
       </c>
@@ -25482,7 +25482,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>757</v>
       </c>
@@ -25541,7 +25541,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>758</v>
       </c>
@@ -25600,7 +25600,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>759</v>
       </c>
@@ -25659,7 +25659,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>760</v>
       </c>
@@ -25718,7 +25718,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>761</v>
       </c>
@@ -25777,7 +25777,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>762</v>
       </c>
@@ -25836,7 +25836,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>763</v>
       </c>
@@ -25895,7 +25895,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>764</v>
       </c>
@@ -25954,7 +25954,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>796</v>
       </c>
@@ -26013,7 +26013,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>797</v>
       </c>
@@ -26072,7 +26072,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>798</v>
       </c>
@@ -26131,7 +26131,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>799</v>
       </c>
@@ -26190,7 +26190,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>800</v>
       </c>
@@ -26249,7 +26249,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>801</v>
       </c>
@@ -26308,7 +26308,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>802</v>
       </c>
@@ -26367,7 +26367,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>803</v>
       </c>
@@ -26426,7 +26426,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>804</v>
       </c>
@@ -26485,7 +26485,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>805</v>
       </c>
@@ -26544,7 +26544,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>806</v>
       </c>
@@ -26603,7 +26603,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>807</v>
       </c>
@@ -26662,7 +26662,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>808</v>
       </c>
@@ -26721,7 +26721,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>809</v>
       </c>
@@ -26780,7 +26780,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>824</v>
       </c>
@@ -26839,7 +26839,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>914</v>
       </c>
@@ -26898,7 +26898,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>915</v>
       </c>
@@ -26957,7 +26957,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>916</v>
       </c>
@@ -27016,7 +27016,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>917</v>
       </c>
@@ -27075,7 +27075,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>918</v>
       </c>
@@ -27134,7 +27134,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>919</v>
       </c>
@@ -27193,7 +27193,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>920</v>
       </c>
@@ -27252,7 +27252,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>921</v>
       </c>
@@ -27311,7 +27311,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>922</v>
       </c>
@@ -27370,7 +27370,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>923</v>
       </c>
@@ -27429,7 +27429,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>924</v>
       </c>
@@ -27488,7 +27488,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>925</v>
       </c>
@@ -27547,7 +27547,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>926</v>
       </c>
@@ -27603,7 +27603,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>1174</v>
       </c>
@@ -27662,7 +27662,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1175</v>
       </c>
@@ -27721,7 +27721,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1176</v>
       </c>
@@ -27780,7 +27780,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1177</v>
       </c>
@@ -27839,7 +27839,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1178</v>
       </c>
@@ -27898,7 +27898,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>1179</v>
       </c>
@@ -27957,7 +27957,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>1180</v>
       </c>
@@ -28016,7 +28016,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>1181</v>
       </c>
@@ -28075,7 +28075,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>1182</v>
       </c>
@@ -28134,7 +28134,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>1183</v>
       </c>
@@ -28193,7 +28193,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1184</v>
       </c>
@@ -28252,7 +28252,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>1185</v>
       </c>
@@ -28311,7 +28311,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>1186</v>
       </c>
@@ -28370,7 +28370,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1187</v>
       </c>
@@ -28429,7 +28429,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>1188</v>
       </c>
@@ -28488,7 +28488,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>1189</v>
       </c>
@@ -28547,7 +28547,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>1190</v>
       </c>
@@ -28600,7 +28600,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>1191</v>
       </c>
@@ -28653,7 +28653,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>1192</v>
       </c>
@@ -28706,7 +28706,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1193</v>
       </c>
@@ -28759,7 +28759,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>1194</v>
       </c>
@@ -28818,7 +28818,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1244</v>
       </c>
@@ -28877,7 +28877,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1245</v>
       </c>
@@ -28930,7 +28930,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>1246</v>
       </c>
@@ -28989,7 +28989,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>1247</v>
       </c>
@@ -29048,7 +29048,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>1248</v>
       </c>
@@ -29098,7 +29098,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>1249</v>
       </c>
@@ -29157,7 +29157,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>1250</v>
       </c>
@@ -29216,7 +29216,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1251</v>
       </c>
@@ -29275,7 +29275,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1252</v>
       </c>
@@ -29334,7 +29334,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>1258</v>
       </c>
@@ -29393,7 +29393,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>1280</v>
       </c>
@@ -29446,7 +29446,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>1284</v>
       </c>
@@ -29505,7 +29505,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>1287</v>
       </c>
@@ -29564,7 +29564,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>1289</v>
       </c>
@@ -29620,7 +29620,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>1297</v>
       </c>
@@ -29679,7 +29679,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>1328</v>
       </c>
@@ -29732,7 +29732,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>1330</v>
       </c>
@@ -29785,7 +29785,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>1332</v>
       </c>
@@ -29844,7 +29844,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1333</v>
       </c>
@@ -29903,7 +29903,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>1334</v>
       </c>
@@ -29962,7 +29962,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1335</v>
       </c>
@@ -30021,7 +30021,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>1336</v>
       </c>
@@ -30074,7 +30074,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>1338</v>
       </c>
@@ -30133,7 +30133,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>1339</v>
       </c>
@@ -30192,7 +30192,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>1340</v>
       </c>
@@ -30245,7 +30245,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1341</v>
       </c>
@@ -30298,7 +30298,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>1342</v>
       </c>
@@ -30351,7 +30351,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1343</v>
       </c>
@@ -30410,7 +30410,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1344</v>
       </c>
@@ -30469,7 +30469,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>1345</v>
       </c>
@@ -30522,7 +30522,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>1346</v>
       </c>
@@ -30575,7 +30575,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>1348</v>
       </c>
@@ -30634,7 +30634,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="189" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>1350</v>
       </c>
@@ -30693,7 +30693,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>1366</v>
       </c>
@@ -30752,7 +30752,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>1368</v>
       </c>
@@ -30805,7 +30805,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1370</v>
       </c>
@@ -30858,7 +30858,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="360" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>1372</v>
       </c>
@@ -30917,7 +30917,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1374</v>
       </c>
@@ -30970,7 +30970,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1376</v>
       </c>
@@ -31029,7 +31029,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>1378</v>
       </c>
@@ -31088,7 +31088,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>1446</v>
       </c>
@@ -31147,7 +31147,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="198" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>1447</v>
       </c>
@@ -31206,7 +31206,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>1448</v>
       </c>
@@ -31265,7 +31265,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1449</v>
       </c>
@@ -31324,7 +31324,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1450</v>
       </c>
@@ -31383,7 +31383,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1451</v>
       </c>
@@ -31442,7 +31442,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>1452</v>
       </c>
@@ -31501,7 +31501,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1453</v>
       </c>
@@ -31560,7 +31560,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>1454</v>
       </c>
@@ -31619,7 +31619,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>1455</v>
       </c>
@@ -31678,7 +31678,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>1456</v>
       </c>
@@ -31731,7 +31731,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>1457</v>
       </c>
@@ -31790,7 +31790,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="209" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1458</v>
       </c>
@@ -31843,7 +31843,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="210" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>1459</v>
       </c>
@@ -31896,7 +31896,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="211" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1460</v>
       </c>
@@ -31949,7 +31949,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="212" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1461</v>
       </c>
@@ -32008,7 +32008,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="213" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1462</v>
       </c>
@@ -32064,7 +32064,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="214" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>1463</v>
       </c>
@@ -32123,7 +32123,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>1464</v>
       </c>
@@ -32182,7 +32182,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="216" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>1465</v>
       </c>
@@ -32241,7 +32241,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="217" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>1466</v>
       </c>
@@ -32300,7 +32300,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="218" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1467</v>
       </c>
@@ -32359,7 +32359,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="219" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1468</v>
       </c>
@@ -32418,7 +32418,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="220" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>1469</v>
       </c>
@@ -32477,7 +32477,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="221" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1470</v>
       </c>
@@ -32536,7 +32536,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="222" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1471</v>
       </c>
@@ -32595,7 +32595,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="223" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>1472</v>
       </c>
@@ -32654,7 +32654,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="224" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>1473</v>
       </c>
@@ -32707,7 +32707,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="225" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>1474</v>
       </c>
@@ -32766,7 +32766,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="226" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>1475</v>
       </c>
@@ -32825,7 +32825,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="227" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1476</v>
       </c>
@@ -32884,7 +32884,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="228" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1477</v>
       </c>
@@ -32943,7 +32943,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="229" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1478</v>
       </c>
@@ -33002,7 +33002,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1479</v>
       </c>
@@ -33061,7 +33061,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1480</v>
       </c>
@@ -33120,7 +33120,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="232" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>1481</v>
       </c>
@@ -33179,7 +33179,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="233" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>1482</v>
       </c>
@@ -33238,7 +33238,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="234" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>1483</v>
       </c>
@@ -33291,7 +33291,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="235" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>1484</v>
       </c>
@@ -33350,7 +33350,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="236" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1485</v>
       </c>
@@ -33409,7 +33409,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="237" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1486</v>
       </c>
@@ -33468,7 +33468,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="238" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1487</v>
       </c>
@@ -33527,7 +33527,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="239" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>1488</v>
       </c>
@@ -33586,7 +33586,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="240" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>1489</v>
       </c>
@@ -33639,7 +33639,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="241" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>1490</v>
       </c>
@@ -33698,7 +33698,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>1493</v>
       </c>
@@ -33757,7 +33757,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="243" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>1495</v>
       </c>
@@ -33816,7 +33816,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="244" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>1497</v>
       </c>
@@ -33875,7 +33875,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1503</v>
       </c>
@@ -33934,7 +33934,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>1505</v>
       </c>
@@ -33993,7 +33993,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="247" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1513</v>
       </c>
@@ -34052,7 +34052,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="248" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>1520</v>
       </c>
@@ -34111,7 +34111,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>1522</v>
       </c>
@@ -34170,7 +34170,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="250" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>1523</v>
       </c>
@@ -34229,7 +34229,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>1524</v>
       </c>
@@ -34285,7 +34285,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>1525</v>
       </c>
@@ -34344,7 +34344,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="253" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>1526</v>
       </c>
@@ -34403,7 +34403,7 @@
         <v>1457</v>
       </c>
     </row>
-    <row r="254" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1527</v>
       </c>
@@ -34462,7 +34462,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="255" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1528</v>
       </c>
@@ -34521,7 +34521,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="256" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>1529</v>
       </c>
@@ -34580,7 +34580,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="257" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>1530</v>
       </c>
@@ -34633,7 +34633,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="258" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>1531</v>
       </c>
@@ -34692,7 +34692,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="259" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>1532</v>
       </c>
@@ -34745,7 +34745,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="260" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>1533</v>
       </c>
@@ -34804,7 +34804,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1534</v>
       </c>
@@ -34863,7 +34863,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>1535</v>
       </c>
@@ -34916,7 +34916,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="263" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1536</v>
       </c>
@@ -34975,7 +34975,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="264" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>1537</v>
       </c>
@@ -35028,7 +35028,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="265" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>1538</v>
       </c>
@@ -35087,7 +35087,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="266" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>1539</v>
       </c>
@@ -35140,7 +35140,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="267" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>1540</v>
       </c>
@@ -35193,7 +35193,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="268" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>1541</v>
       </c>
@@ -35252,7 +35252,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="269" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>1542</v>
       </c>
@@ -35311,7 +35311,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="270" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1543</v>
       </c>
@@ -35370,7 +35370,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="271" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>1544</v>
       </c>
@@ -35423,7 +35423,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="272" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1545</v>
       </c>
@@ -35482,7 +35482,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="273" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>1547</v>
       </c>
@@ -35541,7 +35541,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="274" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>1549</v>
       </c>
@@ -35600,7 +35600,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="275" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>1551</v>
       </c>
@@ -35659,7 +35659,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="276" spans="1:20" ht="330" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>1553</v>
       </c>
@@ -35718,7 +35718,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="277" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1555</v>
       </c>
@@ -35777,7 +35777,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="278" spans="1:20" ht="375" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1557</v>
       </c>
@@ -35836,7 +35836,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="279" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1559</v>
       </c>
@@ -35895,7 +35895,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1561</v>
       </c>
@@ -35948,7 +35948,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="281" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>1563</v>
       </c>
@@ -36001,7 +36001,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="282" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>1565</v>
       </c>
@@ -36060,7 +36060,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="283" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>1567</v>
       </c>
@@ -36119,7 +36119,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="284" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>1569</v>
       </c>
@@ -36178,7 +36178,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="285" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1609</v>
       </c>
@@ -36237,7 +36237,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="286" spans="1:20" ht="330" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1611</v>
       </c>
@@ -36296,7 +36296,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="287" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1613</v>
       </c>
@@ -36355,7 +36355,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="288" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1615</v>
       </c>
@@ -36411,7 +36411,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="289" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>1695</v>
       </c>
@@ -36464,7 +36464,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>1699</v>
       </c>
@@ -36517,7 +36517,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="291" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>1700</v>
       </c>
@@ -36576,7 +36576,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="292" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>1701</v>
       </c>
@@ -36635,7 +36635,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="293" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>1702</v>
       </c>
@@ -36694,7 +36694,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="294" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1703</v>
       </c>
@@ -36753,7 +36753,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="295" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>1704</v>
       </c>
@@ -36812,7 +36812,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="296" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>1705</v>
       </c>
@@ -36871,7 +36871,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="297" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>1706</v>
       </c>
@@ -36930,7 +36930,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="298" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>1707</v>
       </c>
@@ -36989,7 +36989,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="299" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>1709</v>
       </c>
@@ -37048,7 +37048,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="300" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>1710</v>
       </c>
@@ -37107,7 +37107,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="301" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>1711</v>
       </c>
@@ -37166,7 +37166,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="302" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1712</v>
       </c>
@@ -37225,7 +37225,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="303" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>1713</v>
       </c>
@@ -37284,7 +37284,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="304" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>1714</v>
       </c>
@@ -37343,7 +37343,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="305" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>1715</v>
       </c>
@@ -37402,7 +37402,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="306" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>1716</v>
       </c>
@@ -37461,7 +37461,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="307" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>1717</v>
       </c>
@@ -37514,7 +37514,7 @@
         <v>1774</v>
       </c>
     </row>
-    <row r="308" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>1718</v>
       </c>
@@ -37573,7 +37573,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="309" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>1719</v>
       </c>
@@ -37632,7 +37632,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="310" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>1720</v>
       </c>
@@ -37691,7 +37691,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="311" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>1721</v>
       </c>
@@ -37750,7 +37750,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="312" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>1722</v>
       </c>
@@ -37809,7 +37809,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="313" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>1723</v>
       </c>
@@ -37868,7 +37868,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="314" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>1724</v>
       </c>
@@ -37927,7 +37927,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="315" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>1725</v>
       </c>
@@ -37986,7 +37986,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="316" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>1726</v>
       </c>
@@ -38045,7 +38045,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="317" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>1727</v>
       </c>
@@ -38104,7 +38104,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="318" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1728</v>
       </c>
@@ -38163,7 +38163,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="319" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>1729</v>
       </c>
@@ -38222,7 +38222,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="320" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>1765</v>
       </c>
@@ -38275,7 +38275,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="321" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>1767</v>
       </c>
@@ -38328,7 +38328,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="322" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>1779</v>
       </c>
@@ -38378,7 +38378,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="323" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>1782</v>
       </c>
@@ -38428,7 +38428,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="324" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>1786</v>
       </c>
@@ -38481,7 +38481,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="325" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>1795</v>
       </c>
@@ -38540,7 +38540,7 @@
         <v>1868</v>
       </c>
     </row>
-    <row r="326" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>1796</v>
       </c>
@@ -38599,7 +38599,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="327" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>1797</v>
       </c>
@@ -38658,7 +38658,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="328" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>1798</v>
       </c>
@@ -38717,7 +38717,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="329" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>1799</v>
       </c>
@@ -38773,7 +38773,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="330" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>1800</v>
       </c>
@@ -38832,7 +38832,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="331" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>1801</v>
       </c>
@@ -38891,7 +38891,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="332" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>1802</v>
       </c>
@@ -38950,7 +38950,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="333" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>1803</v>
       </c>
@@ -39009,7 +39009,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="334" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>1804</v>
       </c>
@@ -39068,7 +39068,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="335" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>1805</v>
       </c>
@@ -39127,7 +39127,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="336" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>1806</v>
       </c>
@@ -39186,7 +39186,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="337" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>1807</v>
       </c>
@@ -39245,7 +39245,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="338" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>1808</v>
       </c>
@@ -39304,7 +39304,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="339" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>1810</v>
       </c>
@@ -39363,7 +39363,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="340" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>1811</v>
       </c>
@@ -39422,7 +39422,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="341" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>1812</v>
       </c>
@@ -39481,7 +39481,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="342" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>1813</v>
       </c>
@@ -39540,7 +39540,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="343" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>1814</v>
       </c>
@@ -39599,7 +39599,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>1815</v>
       </c>
@@ -39658,7 +39658,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="345" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>1816</v>
       </c>
@@ -39717,7 +39717,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="346" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>1817</v>
       </c>
@@ -39776,7 +39776,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="347" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>1818</v>
       </c>
@@ -39835,7 +39835,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="348" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>1819</v>
       </c>
@@ -39894,7 +39894,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="349" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>1820</v>
       </c>
@@ -39953,7 +39953,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="350" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>1821</v>
       </c>
@@ -40012,7 +40012,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="351" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>1822</v>
       </c>
@@ -40071,7 +40071,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="352" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>1823</v>
       </c>
@@ -40130,7 +40130,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="353" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>1924</v>
       </c>
@@ -40189,7 +40189,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="354" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>1925</v>
       </c>
@@ -40248,7 +40248,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="355" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>1926</v>
       </c>
@@ -40307,7 +40307,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="356" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>1927</v>
       </c>
@@ -40366,7 +40366,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="357" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>1928</v>
       </c>
@@ -40425,7 +40425,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="358" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>1929</v>
       </c>
@@ -40484,7 +40484,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="359" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>1930</v>
       </c>
@@ -40531,7 +40531,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="360" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>1931</v>
       </c>
@@ -40590,7 +40590,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="361" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>1932</v>
       </c>
@@ -40649,7 +40649,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="362" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>1933</v>
       </c>
@@ -40702,7 +40702,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="363" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>1934</v>
       </c>
@@ -40761,7 +40761,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="364" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>1935</v>
       </c>
@@ -40820,7 +40820,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="365" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>1936</v>
       </c>
@@ -40879,7 +40879,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="366" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>1937</v>
       </c>
@@ -40938,7 +40938,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="367" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>1938</v>
       </c>
@@ -40997,7 +40997,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="368" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>1939</v>
       </c>
@@ -41056,7 +41056,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="369" spans="1:20" ht="315" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>1940</v>
       </c>
@@ -41115,7 +41115,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="370" spans="1:20" ht="360" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>1941</v>
       </c>
@@ -41174,7 +41174,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="371" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>1942</v>
       </c>
@@ -41233,7 +41233,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="372" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>1943</v>
       </c>
@@ -41292,7 +41292,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="373" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1944</v>
       </c>
@@ -41351,7 +41351,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="374" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1945</v>
       </c>
@@ -41410,7 +41410,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="375" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>1946</v>
       </c>
@@ -41469,7 +41469,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="376" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>1947</v>
       </c>
@@ -41528,7 +41528,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="377" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>1978</v>
       </c>
@@ -41581,7 +41581,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="378" spans="1:20" ht="180" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>1979</v>
       </c>
@@ -41634,7 +41634,7 @@
         <v>2152</v>
       </c>
     </row>
-    <row r="379" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>1980</v>
       </c>
@@ -41687,7 +41687,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="380" spans="1:20" ht="180" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>1981</v>
       </c>
@@ -41740,7 +41740,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="381" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>1982</v>
       </c>
@@ -41793,7 +41793,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="382" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>1983</v>
       </c>
@@ -41846,7 +41846,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="383" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>1984</v>
       </c>
@@ -41899,7 +41899,7 @@
         <v>2174</v>
       </c>
     </row>
-    <row r="384" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>1985</v>
       </c>
@@ -41952,7 +41952,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="385" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>1986</v>
       </c>
@@ -42005,7 +42005,7 @@
         <v>2184</v>
       </c>
     </row>
-    <row r="386" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>1987</v>
       </c>
@@ -42064,7 +42064,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="387" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>1988</v>
       </c>
@@ -42123,7 +42123,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="388" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>1989</v>
       </c>
@@ -42173,7 +42173,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="389" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>1990</v>
       </c>
@@ -42226,7 +42226,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="390" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>1991</v>
       </c>
@@ -42285,7 +42285,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="391" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>1992</v>
       </c>
@@ -42338,7 +42338,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="392" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>1993</v>
       </c>
@@ -42391,7 +42391,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="393" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>1994</v>
       </c>
@@ -42450,7 +42450,7 @@
         <v>2227</v>
       </c>
     </row>
-    <row r="394" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>1995</v>
       </c>
@@ -42503,7 +42503,7 @@
         <v>2233</v>
       </c>
     </row>
-    <row r="395" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>1996</v>
       </c>
@@ -42556,7 +42556,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="396" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>1997</v>
       </c>
@@ -42615,7 +42615,7 @@
         <v>2243</v>
       </c>
     </row>
-    <row r="397" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>1998</v>
       </c>
@@ -42668,7 +42668,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="398" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>1999</v>
       </c>
@@ -42727,7 +42727,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="399" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>2000</v>
       </c>
@@ -42780,7 +42780,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="400" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>2001</v>
       </c>
@@ -42833,7 +42833,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="401" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>2002</v>
       </c>
@@ -42886,7 +42886,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="402" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>2003</v>
       </c>
@@ -42939,7 +42939,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="403" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>2004</v>
       </c>
@@ -42992,7 +42992,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="404" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>2005</v>
       </c>
@@ -43045,7 +43045,7 @@
         <v>2285</v>
       </c>
     </row>
-    <row r="405" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>2006</v>
       </c>
@@ -43098,7 +43098,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="406" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>2007</v>
       </c>
@@ -43151,7 +43151,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="407" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>2008</v>
       </c>
@@ -43210,7 +43210,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="408" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>2009</v>
       </c>
@@ -43269,7 +43269,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="409" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>2010</v>
       </c>
@@ -43322,7 +43322,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="410" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>2011</v>
       </c>
@@ -43375,7 +43375,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="411" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>2012</v>
       </c>
@@ -43434,7 +43434,7 @@
         <v>2323</v>
       </c>
     </row>
-    <row r="412" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>2013</v>
       </c>
@@ -43487,7 +43487,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="413" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>2014</v>
       </c>
@@ -43540,7 +43540,7 @@
         <v>2335</v>
       </c>
     </row>
-    <row r="414" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>2015</v>
       </c>
@@ -43593,7 +43593,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="415" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>2016</v>
       </c>
@@ -43646,7 +43646,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="416" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>2017</v>
       </c>
@@ -43699,7 +43699,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="417" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>2018</v>
       </c>
@@ -43752,7 +43752,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="418" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>2019</v>
       </c>
@@ -43805,7 +43805,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="419" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>2020</v>
       </c>
@@ -43864,7 +43864,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="420" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>2021</v>
       </c>
@@ -43917,7 +43917,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="421" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>2022</v>
       </c>
@@ -43970,7 +43970,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="422" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>2023</v>
       </c>
@@ -44023,7 +44023,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="423" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>2024</v>
       </c>
@@ -44076,7 +44076,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="424" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>2025</v>
       </c>
@@ -44129,7 +44129,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="425" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>2026</v>
       </c>
@@ -44182,7 +44182,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="426" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>2027</v>
       </c>
@@ -44235,7 +44235,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="427" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>2028</v>
       </c>
@@ -44288,7 +44288,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="428" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>2029</v>
       </c>
@@ -44341,7 +44341,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="429" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>2030</v>
       </c>
@@ -44394,7 +44394,7 @@
         <v>2417</v>
       </c>
     </row>
-    <row r="430" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>2031</v>
       </c>
@@ -44447,7 +44447,7 @@
         <v>2422</v>
       </c>
     </row>
-    <row r="431" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>2032</v>
       </c>
@@ -44506,7 +44506,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="432" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>2033</v>
       </c>
@@ -44559,7 +44559,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="433" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>2034</v>
       </c>
@@ -44612,7 +44612,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="434" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>2035</v>
       </c>
@@ -44665,7 +44665,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="435" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>2036</v>
       </c>
@@ -44724,7 +44724,7 @@
         <v>2447</v>
       </c>
     </row>
-    <row r="436" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>2037</v>
       </c>
@@ -44777,7 +44777,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="437" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>2038</v>
       </c>
@@ -44830,7 +44830,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="438" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>2039</v>
       </c>
@@ -44889,7 +44889,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="439" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>2040</v>
       </c>
@@ -44942,7 +44942,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="440" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>2041</v>
       </c>
@@ -44995,7 +44995,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="441" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>2042</v>
       </c>
@@ -45048,7 +45048,7 @@
         <v>2479</v>
       </c>
     </row>
-    <row r="442" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>2043</v>
       </c>
@@ -45101,7 +45101,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="443" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>2044</v>
       </c>
@@ -45154,7 +45154,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="444" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>2045</v>
       </c>
@@ -45207,7 +45207,7 @@
         <v>2494</v>
       </c>
     </row>
-    <row r="445" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>2046</v>
       </c>
@@ -45260,7 +45260,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="446" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>2047</v>
       </c>
@@ -45313,7 +45313,7 @@
         <v>2504</v>
       </c>
     </row>
-    <row r="447" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>2048</v>
       </c>
@@ -45366,7 +45366,7 @@
         <v>2509</v>
       </c>
     </row>
-    <row r="448" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>2049</v>
       </c>
@@ -45425,7 +45425,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="449" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>2050</v>
       </c>
@@ -45484,7 +45484,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="450" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>2051</v>
       </c>
@@ -45543,7 +45543,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="451" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>2052</v>
       </c>
@@ -45596,7 +45596,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="452" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>2053</v>
       </c>
@@ -45649,7 +45649,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="453" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>2054</v>
       </c>
@@ -45702,7 +45702,7 @@
         <v>2543</v>
       </c>
     </row>
-    <row r="454" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>2055</v>
       </c>
@@ -45755,7 +45755,7 @@
         <v>2548</v>
       </c>
     </row>
-    <row r="455" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>2056</v>
       </c>
@@ -45808,7 +45808,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="456" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>2057</v>
       </c>
@@ -45867,7 +45867,7 @@
         <v>2558</v>
       </c>
     </row>
-    <row r="457" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>2058</v>
       </c>
@@ -45920,7 +45920,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="458" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>2059</v>
       </c>
@@ -45979,7 +45979,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="459" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>2060</v>
       </c>
@@ -46032,7 +46032,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="460" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>2061</v>
       </c>
@@ -46091,7 +46091,7 @@
         <v>2580</v>
       </c>
     </row>
-    <row r="461" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>2062</v>
       </c>
@@ -46144,7 +46144,7 @@
         <v>2586</v>
       </c>
     </row>
-    <row r="462" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>2063</v>
       </c>
@@ -46197,7 +46197,7 @@
         <v>2591</v>
       </c>
     </row>
-    <row r="463" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>2064</v>
       </c>
@@ -46250,7 +46250,7 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="464" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>2065</v>
       </c>
@@ -46303,7 +46303,7 @@
         <v>2601</v>
       </c>
     </row>
-    <row r="465" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>2066</v>
       </c>
@@ -46356,7 +46356,7 @@
         <v>2606</v>
       </c>
     </row>
-    <row r="466" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>2067</v>
       </c>
@@ -46409,7 +46409,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="467" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>2068</v>
       </c>
@@ -46462,7 +46462,7 @@
         <v>2616</v>
       </c>
     </row>
-    <row r="468" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>2069</v>
       </c>
@@ -46515,7 +46515,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="469" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>2070</v>
       </c>
@@ -46568,7 +46568,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="470" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>2071</v>
       </c>
@@ -46621,7 +46621,7 @@
         <v>2632</v>
       </c>
     </row>
-    <row r="471" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>2072</v>
       </c>
@@ -46674,7 +46674,7 @@
         <v>2637</v>
       </c>
     </row>
-    <row r="472" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>2073</v>
       </c>
@@ -46727,7 +46727,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="473" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>2074</v>
       </c>
@@ -46780,7 +46780,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="474" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>2075</v>
       </c>
@@ -46839,7 +46839,7 @@
         <v>2652</v>
       </c>
     </row>
-    <row r="475" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>2076</v>
       </c>
@@ -46892,7 +46892,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="476" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>2077</v>
       </c>
@@ -46945,7 +46945,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="477" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>2078</v>
       </c>
@@ -46998,7 +46998,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="478" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>2079</v>
       </c>
@@ -47051,7 +47051,7 @@
         <v>2673</v>
       </c>
     </row>
-    <row r="479" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>2080</v>
       </c>
@@ -47104,7 +47104,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="480" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>2081</v>
       </c>
@@ -47157,7 +47157,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="481" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>2082</v>
       </c>
@@ -47210,7 +47210,7 @@
         <v>2688</v>
       </c>
     </row>
-    <row r="482" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>2083</v>
       </c>
@@ -47263,7 +47263,7 @@
         <v>2693</v>
       </c>
     </row>
-    <row r="483" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>2084</v>
       </c>
@@ -47316,7 +47316,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="484" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>2085</v>
       </c>
@@ -47369,7 +47369,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="485" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>2086</v>
       </c>
@@ -47422,7 +47422,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="486" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>2087</v>
       </c>
@@ -47475,7 +47475,7 @@
         <v>2712</v>
       </c>
     </row>
-    <row r="487" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>2088</v>
       </c>
@@ -47528,7 +47528,7 @@
         <v>2718</v>
       </c>
     </row>
-    <row r="488" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>2089</v>
       </c>
@@ -47581,7 +47581,7 @@
         <v>2723</v>
       </c>
     </row>
-    <row r="489" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>2090</v>
       </c>
@@ -47634,7 +47634,7 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="490" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>2091</v>
       </c>
@@ -47687,7 +47687,7 @@
         <v>2733</v>
       </c>
     </row>
-    <row r="491" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>2092</v>
       </c>
@@ -47740,7 +47740,7 @@
         <v>2738</v>
       </c>
     </row>
-    <row r="492" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>2093</v>
       </c>
@@ -47793,7 +47793,7 @@
         <v>2743</v>
       </c>
     </row>
-    <row r="493" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>2094</v>
       </c>
@@ -47846,7 +47846,7 @@
         <v>2748</v>
       </c>
     </row>
-    <row r="494" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>2095</v>
       </c>
@@ -47899,7 +47899,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="495" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>2096</v>
       </c>
@@ -47952,7 +47952,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="496" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>2097</v>
       </c>
@@ -48005,7 +48005,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="497" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>2098</v>
       </c>
@@ -48064,7 +48064,7 @@
         <v>2768</v>
       </c>
     </row>
-    <row r="498" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>2099</v>
       </c>
@@ -48123,7 +48123,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="499" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>2100</v>
       </c>
@@ -48176,7 +48176,7 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="500" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>2101</v>
       </c>
@@ -48229,7 +48229,7 @@
         <v>2785</v>
       </c>
     </row>
-    <row r="501" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>2102</v>
       </c>
@@ -48282,7 +48282,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="502" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>2103</v>
       </c>
@@ -48335,7 +48335,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="503" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>2104</v>
       </c>
@@ -48388,7 +48388,7 @@
         <v>2801</v>
       </c>
     </row>
-    <row r="504" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>2105</v>
       </c>
@@ -48441,7 +48441,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="505" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>2106</v>
       </c>
@@ -48494,7 +48494,7 @@
         <v>2811</v>
       </c>
     </row>
-    <row r="506" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>2107</v>
       </c>
@@ -48547,7 +48547,7 @@
         <v>2816</v>
       </c>
     </row>
-    <row r="507" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>2108</v>
       </c>
@@ -48600,7 +48600,7 @@
         <v>2821</v>
       </c>
     </row>
-    <row r="508" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>2262</v>
       </c>
@@ -48659,7 +48659,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="509" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>2263</v>
       </c>
@@ -48718,7 +48718,7 @@
         <v>2832</v>
       </c>
     </row>
-    <row r="510" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>2264</v>
       </c>
@@ -48777,7 +48777,7 @@
         <v>2837</v>
       </c>
     </row>
-    <row r="511" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>2265</v>
       </c>
@@ -48836,7 +48836,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="512" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>2266</v>
       </c>
@@ -48895,7 +48895,7 @@
         <v>2848</v>
       </c>
     </row>
-    <row r="513" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>2267</v>
       </c>
@@ -48954,7 +48954,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="514" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>2268</v>
       </c>
@@ -49013,7 +49013,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="515" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>2269</v>
       </c>
@@ -49060,7 +49060,7 @@
         <v>2864</v>
       </c>
     </row>
-    <row r="516" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>2270</v>
       </c>
@@ -49119,7 +49119,7 @@
         <v>2870</v>
       </c>
     </row>
-    <row r="517" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>2271</v>
       </c>
@@ -49178,7 +49178,7 @@
         <v>2876</v>
       </c>
     </row>
-    <row r="518" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>2272</v>
       </c>
@@ -49237,7 +49237,7 @@
         <v>2881</v>
       </c>
     </row>
-    <row r="519" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>2273</v>
       </c>
@@ -49296,7 +49296,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="520" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>2274</v>
       </c>
@@ -49355,7 +49355,7 @@
         <v>2892</v>
       </c>
     </row>
-    <row r="521" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>2275</v>
       </c>
@@ -49414,7 +49414,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="522" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>2276</v>
       </c>
@@ -49473,7 +49473,7 @@
         <v>2902</v>
       </c>
     </row>
-    <row r="523" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>2277</v>
       </c>
@@ -49532,7 +49532,7 @@
         <v>2907</v>
       </c>
     </row>
-    <row r="524" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>2278</v>
       </c>
@@ -49591,7 +49591,7 @@
         <v>2912</v>
       </c>
     </row>
-    <row r="525" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>2279</v>
       </c>
@@ -49650,7 +49650,7 @@
         <v>2917</v>
       </c>
     </row>
-    <row r="526" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>2280</v>
       </c>
@@ -49709,7 +49709,7 @@
         <v>2922</v>
       </c>
     </row>
-    <row r="527" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>2281</v>
       </c>
@@ -49762,7 +49762,7 @@
         <v>2927</v>
       </c>
     </row>
-    <row r="528" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>2282</v>
       </c>
@@ -49821,7 +49821,7 @@
         <v>2932</v>
       </c>
     </row>
-    <row r="529" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>2283</v>
       </c>
@@ -49874,7 +49874,7 @@
         <v>2937</v>
       </c>
     </row>
-    <row r="530" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>2284</v>
       </c>
@@ -49933,7 +49933,7 @@
         <v>2942</v>
       </c>
     </row>
-    <row r="531" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>2285</v>
       </c>
@@ -49992,7 +49992,7 @@
         <v>2949</v>
       </c>
     </row>
-    <row r="532" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>2286</v>
       </c>
@@ -50051,7 +50051,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="533" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>2454</v>
       </c>
@@ -50110,7 +50110,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="534" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>2455</v>
       </c>
@@ -50169,7 +50169,7 @@
         <v>2967</v>
       </c>
     </row>
-    <row r="535" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>2456</v>
       </c>
@@ -50228,7 +50228,7 @@
         <v>2973</v>
       </c>
     </row>
-    <row r="536" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>2457</v>
       </c>
@@ -50287,7 +50287,7 @@
         <v>2978</v>
       </c>
     </row>
-    <row r="537" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>2458</v>
       </c>
@@ -50346,7 +50346,7 @@
         <v>2983</v>
       </c>
     </row>
-    <row r="538" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>2459</v>
       </c>
@@ -50405,7 +50405,7 @@
         <v>2989</v>
       </c>
     </row>
-    <row r="539" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>2460</v>
       </c>
@@ -50464,7 +50464,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="540" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>2462</v>
       </c>
@@ -50523,7 +50523,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="541" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>2463</v>
       </c>
@@ -50582,7 +50582,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="542" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>2464</v>
       </c>
@@ -50641,7 +50641,7 @@
         <v>3011</v>
       </c>
     </row>
-    <row r="543" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>2465</v>
       </c>
@@ -50700,7 +50700,7 @@
         <v>3016</v>
       </c>
     </row>
-    <row r="544" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>2466</v>
       </c>
@@ -50759,7 +50759,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="545" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>2467</v>
       </c>
@@ -50812,7 +50812,7 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="546" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>2468</v>
       </c>
@@ -50871,7 +50871,7 @@
         <v>3031</v>
       </c>
     </row>
-    <row r="547" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>2469</v>
       </c>
@@ -50930,7 +50930,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="548" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>2470</v>
       </c>
@@ -50989,7 +50989,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="549" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>2471</v>
       </c>
@@ -51048,7 +51048,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="550" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>2472</v>
       </c>
@@ -51107,7 +51107,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="551" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>2473</v>
       </c>
@@ -51166,7 +51166,7 @@
         <v>3060</v>
       </c>
     </row>
-    <row r="552" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>2474</v>
       </c>
@@ -51225,7 +51225,7 @@
         <v>3066</v>
       </c>
     </row>
-    <row r="553" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>2475</v>
       </c>
@@ -51284,7 +51284,7 @@
         <v>3072</v>
       </c>
     </row>
-    <row r="554" spans="1:20" ht="330" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>2476</v>
       </c>
@@ -51337,7 +51337,7 @@
         <v>3078</v>
       </c>
     </row>
-    <row r="555" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>2477</v>
       </c>
@@ -51396,7 +51396,7 @@
         <v>3083</v>
       </c>
     </row>
-    <row r="556" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>2478</v>
       </c>
@@ -51455,7 +51455,7 @@
         <v>3088</v>
       </c>
     </row>
-    <row r="557" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>2479</v>
       </c>
@@ -51514,7 +51514,7 @@
         <v>3094</v>
       </c>
     </row>
-    <row r="558" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>2480</v>
       </c>
@@ -51567,7 +51567,7 @@
         <v>3099</v>
       </c>
     </row>
-    <row r="559" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>2481</v>
       </c>
@@ -51620,7 +51620,7 @@
         <v>3104</v>
       </c>
     </row>
-    <row r="560" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>2482</v>
       </c>
@@ -51679,7 +51679,7 @@
         <v>3109</v>
       </c>
     </row>
-    <row r="561" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>2483</v>
       </c>
@@ -51732,7 +51732,7 @@
         <v>3114</v>
       </c>
     </row>
-    <row r="562" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>2484</v>
       </c>
@@ -51791,7 +51791,7 @@
         <v>3119</v>
       </c>
     </row>
-    <row r="563" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>2486</v>
       </c>
@@ -51844,7 +51844,7 @@
         <v>3124</v>
       </c>
     </row>
-    <row r="564" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>2601</v>
       </c>
@@ -51903,7 +51903,7 @@
         <v>3129</v>
       </c>
     </row>
-    <row r="565" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>2602</v>
       </c>
@@ -51962,7 +51962,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="566" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>2603</v>
       </c>
@@ -52021,7 +52021,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="567" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>2604</v>
       </c>
@@ -52080,7 +52080,7 @@
         <v>3146</v>
       </c>
     </row>
-    <row r="568" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>2605</v>
       </c>
@@ -52139,7 +52139,7 @@
         <v>3151</v>
       </c>
     </row>
-    <row r="569" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>2606</v>
       </c>
@@ -52198,7 +52198,7 @@
         <v>3156</v>
       </c>
     </row>
-    <row r="570" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>2607</v>
       </c>
@@ -52257,7 +52257,7 @@
         <v>3161</v>
       </c>
     </row>
-    <row r="571" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>2608</v>
       </c>
@@ -52316,7 +52316,7 @@
         <v>3166</v>
       </c>
     </row>
-    <row r="572" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>2609</v>
       </c>
@@ -52375,7 +52375,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="573" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>2610</v>
       </c>
@@ -52434,7 +52434,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="574" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>2611</v>
       </c>
@@ -52493,7 +52493,7 @@
         <v>3181</v>
       </c>
     </row>
-    <row r="575" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>2612</v>
       </c>
@@ -52552,7 +52552,7 @@
         <v>3186</v>
       </c>
     </row>
-    <row r="576" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>2613</v>
       </c>
@@ -52611,7 +52611,7 @@
         <v>3192</v>
       </c>
     </row>
-    <row r="577" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>2614</v>
       </c>
@@ -52670,7 +52670,7 @@
         <v>3198</v>
       </c>
     </row>
-    <row r="578" spans="1:20" ht="150" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>2615</v>
       </c>
@@ -52729,7 +52729,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="579" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>2616</v>
       </c>
@@ -52788,7 +52788,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="580" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>2617</v>
       </c>
@@ -52847,7 +52847,7 @@
         <v>3216</v>
       </c>
     </row>
-    <row r="581" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>2618</v>
       </c>
@@ -52906,7 +52906,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="582" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>2619</v>
       </c>
@@ -52965,7 +52965,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="583" spans="1:20" ht="180" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>2620</v>
       </c>
@@ -53024,7 +53024,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="584" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>2646</v>
       </c>
@@ -53083,7 +53083,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="585" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>2684</v>
       </c>
@@ -53142,7 +53142,7 @@
         <v>3244</v>
       </c>
     </row>
-    <row r="586" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>2685</v>
       </c>
@@ -53201,7 +53201,7 @@
         <v>3251</v>
       </c>
     </row>
-    <row r="587" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>2686</v>
       </c>
@@ -53260,7 +53260,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="588" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>2687</v>
       </c>
@@ -53319,7 +53319,7 @@
         <v>3262</v>
       </c>
     </row>
-    <row r="589" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>2688</v>
       </c>
@@ -53378,7 +53378,7 @@
         <v>3267</v>
       </c>
     </row>
-    <row r="590" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>2689</v>
       </c>
@@ -53437,7 +53437,7 @@
         <v>3272</v>
       </c>
     </row>
-    <row r="591" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>2690</v>
       </c>
@@ -53496,7 +53496,7 @@
         <v>3277</v>
       </c>
     </row>
-    <row r="592" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>2691</v>
       </c>
@@ -53555,7 +53555,7 @@
         <v>3283</v>
       </c>
     </row>
-    <row r="593" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>2694</v>
       </c>
@@ -53614,7 +53614,7 @@
         <v>3289</v>
       </c>
     </row>
-    <row r="594" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>2695</v>
       </c>
@@ -53673,7 +53673,7 @@
         <v>3295</v>
       </c>
     </row>
-    <row r="595" spans="1:20" ht="300" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>2696</v>
       </c>
@@ -53732,7 +53732,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="596" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>2697</v>
       </c>
@@ -53791,7 +53791,7 @@
         <v>3305</v>
       </c>
     </row>
-    <row r="597" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>2698</v>
       </c>
@@ -53850,7 +53850,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="598" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>2699</v>
       </c>
@@ -53909,7 +53909,7 @@
         <v>3316</v>
       </c>
     </row>
-    <row r="599" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>2700</v>
       </c>
@@ -53968,7 +53968,7 @@
         <v>3321</v>
       </c>
     </row>
-    <row r="600" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>2701</v>
       </c>
@@ -54027,7 +54027,7 @@
         <v>3327</v>
       </c>
     </row>
-    <row r="601" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>2702</v>
       </c>
@@ -54086,7 +54086,7 @@
         <v>3333</v>
       </c>
     </row>
-    <row r="602" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>2703</v>
       </c>
@@ -54145,7 +54145,7 @@
         <v>3339</v>
       </c>
     </row>
-    <row r="603" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>2704</v>
       </c>
@@ -54204,7 +54204,7 @@
         <v>3345</v>
       </c>
     </row>
-    <row r="604" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>2705</v>
       </c>
@@ -54263,7 +54263,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="605" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>2854</v>
       </c>
@@ -54322,7 +54322,7 @@
         <v>3355</v>
       </c>
     </row>
-    <row r="606" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606">
         <v>2855</v>
       </c>
@@ -54381,7 +54381,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="607" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607">
         <v>2856</v>
       </c>
@@ -54440,7 +54440,7 @@
         <v>3368</v>
       </c>
     </row>
-    <row r="608" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608">
         <v>2857</v>
       </c>
@@ -54499,7 +54499,7 @@
         <v>3374</v>
       </c>
     </row>
-    <row r="609" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609">
         <v>2858</v>
       </c>
@@ -54558,7 +54558,7 @@
         <v>3379</v>
       </c>
     </row>
-    <row r="610" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610">
         <v>2860</v>
       </c>
@@ -54617,7 +54617,7 @@
         <v>3385</v>
       </c>
     </row>
-    <row r="611" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611">
         <v>2861</v>
       </c>
@@ -54676,7 +54676,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="612" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612">
         <v>2862</v>
       </c>
@@ -54735,7 +54735,7 @@
         <v>3395</v>
       </c>
     </row>
-    <row r="613" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613">
         <v>2863</v>
       </c>
@@ -54794,7 +54794,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="614" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614">
         <v>2864</v>
       </c>
@@ -54853,7 +54853,7 @@
         <v>3406</v>
       </c>
     </row>
-    <row r="615" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615">
         <v>2865</v>
       </c>
@@ -54912,7 +54912,7 @@
         <v>3411</v>
       </c>
     </row>
-    <row r="616" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616">
         <v>2866</v>
       </c>
@@ -54971,7 +54971,7 @@
         <v>3416</v>
       </c>
     </row>
-    <row r="617" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617">
         <v>2867</v>
       </c>
@@ -55030,7 +55030,7 @@
         <v>3421</v>
       </c>
     </row>
-    <row r="618" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618">
         <v>2868</v>
       </c>
@@ -55089,7 +55089,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="619" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619">
         <v>2869</v>
       </c>
@@ -55148,7 +55148,7 @@
         <v>3432</v>
       </c>
     </row>
-    <row r="620" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620">
         <v>2870</v>
       </c>
@@ -55207,7 +55207,7 @@
         <v>3438</v>
       </c>
     </row>
-    <row r="621" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621">
         <v>2871</v>
       </c>
@@ -55266,7 +55266,7 @@
         <v>3444</v>
       </c>
     </row>
-    <row r="622" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622">
         <v>2872</v>
       </c>
@@ -55325,7 +55325,7 @@
         <v>3449</v>
       </c>
     </row>
-    <row r="623" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623">
         <v>2873</v>
       </c>
@@ -55384,7 +55384,7 @@
         <v>3454</v>
       </c>
     </row>
-    <row r="624" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624">
         <v>2874</v>
       </c>
@@ -55443,7 +55443,7 @@
         <v>3459</v>
       </c>
     </row>
-    <row r="625" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625">
         <v>2875</v>
       </c>
@@ -55502,7 +55502,7 @@
         <v>3464</v>
       </c>
     </row>
-    <row r="626" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626">
         <v>2876</v>
       </c>
@@ -55561,7 +55561,7 @@
         <v>3469</v>
       </c>
     </row>
-    <row r="627" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627">
         <v>2877</v>
       </c>
@@ -55620,7 +55620,7 @@
         <v>3475</v>
       </c>
     </row>
-    <row r="628" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628">
         <v>2878</v>
       </c>
@@ -55679,7 +55679,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="629" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629">
         <v>2879</v>
       </c>
@@ -55738,7 +55738,7 @@
         <v>3486</v>
       </c>
     </row>
-    <row r="630" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630">
         <v>2880</v>
       </c>
@@ -55797,7 +55797,7 @@
         <v>3491</v>
       </c>
     </row>
-    <row r="631" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631">
         <v>2882</v>
       </c>
@@ -55856,7 +55856,7 @@
         <v>3496</v>
       </c>
     </row>
-    <row r="632" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632">
         <v>2883</v>
       </c>
@@ -55915,7 +55915,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="633" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633">
         <v>2884</v>
       </c>
@@ -55974,7 +55974,7 @@
         <v>3506</v>
       </c>
     </row>
-    <row r="634" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634">
         <v>2885</v>
       </c>
@@ -56033,7 +56033,7 @@
         <v>3511</v>
       </c>
     </row>
-    <row r="635" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635">
         <v>2886</v>
       </c>
@@ -56092,7 +56092,7 @@
         <v>3516</v>
       </c>
     </row>
-    <row r="636" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636">
         <v>2887</v>
       </c>
@@ -56151,7 +56151,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="637" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637">
         <v>2888</v>
       </c>
@@ -56210,7 +56210,7 @@
         <v>3527</v>
       </c>
     </row>
-    <row r="638" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638">
         <v>3932</v>
       </c>
@@ -56269,7 +56269,7 @@
         <v>3532</v>
       </c>
     </row>
-    <row r="639" spans="1:20" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639">
         <v>3933</v>
       </c>
@@ -56328,7 +56328,7 @@
         <v>3541</v>
       </c>
     </row>
-    <row r="640" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640">
         <v>3934</v>
       </c>
@@ -56387,7 +56387,7 @@
         <v>3547</v>
       </c>
     </row>
-    <row r="641" spans="1:20" ht="195" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641">
         <v>3935</v>
       </c>
@@ -56446,7 +56446,7 @@
         <v>3552</v>
       </c>
     </row>
-    <row r="642" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642">
         <v>3936</v>
       </c>
@@ -56505,7 +56505,7 @@
         <v>3557</v>
       </c>
     </row>
-    <row r="643" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643">
         <v>3937</v>
       </c>
@@ -56564,7 +56564,7 @@
         <v>3564</v>
       </c>
     </row>
-    <row r="644" spans="1:20" ht="330" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644">
         <v>3938</v>
       </c>
@@ -56623,7 +56623,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="645" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645">
         <v>3940</v>
       </c>
@@ -56682,7 +56682,7 @@
         <v>3575</v>
       </c>
     </row>
-    <row r="646" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646">
         <v>3941</v>
       </c>
@@ -56741,7 +56741,7 @@
         <v>3581</v>
       </c>
     </row>
-    <row r="647" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647">
         <v>3942</v>
       </c>
@@ -56800,7 +56800,7 @@
         <v>3586</v>
       </c>
     </row>
-    <row r="648" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648">
         <v>3943</v>
       </c>
@@ -56859,7 +56859,7 @@
         <v>3592</v>
       </c>
     </row>
-    <row r="649" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649">
         <v>3944</v>
       </c>
@@ -56918,7 +56918,7 @@
         <v>3597</v>
       </c>
     </row>
-    <row r="650" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650">
         <v>3946</v>
       </c>
@@ -56977,7 +56977,7 @@
         <v>3603</v>
       </c>
     </row>
-    <row r="651" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651">
         <v>3947</v>
       </c>
@@ -57036,7 +57036,7 @@
         <v>3608</v>
       </c>
     </row>
-    <row r="652" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652">
         <v>3948</v>
       </c>
@@ -57095,7 +57095,7 @@
         <v>3614</v>
       </c>
     </row>
-    <row r="653" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653">
         <v>3949</v>
       </c>
@@ -57154,7 +57154,7 @@
         <v>3619</v>
       </c>
     </row>
-    <row r="654" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654">
         <v>3950</v>
       </c>
@@ -57213,7 +57213,7 @@
         <v>3625</v>
       </c>
     </row>
-    <row r="655" spans="1:20" ht="345" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655">
         <v>3951</v>
       </c>
@@ -57272,7 +57272,7 @@
         <v>3630</v>
       </c>
     </row>
-    <row r="656" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656">
         <v>3952</v>
       </c>
@@ -57331,7 +57331,7 @@
         <v>3636</v>
       </c>
     </row>
-    <row r="657" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657">
         <v>3953</v>
       </c>
@@ -57390,7 +57390,7 @@
         <v>3642</v>
       </c>
     </row>
-    <row r="658" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658">
         <v>4029</v>
       </c>
@@ -57449,7 +57449,7 @@
         <v>3647</v>
       </c>
     </row>
-    <row r="659" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659">
         <v>4030</v>
       </c>
@@ -57508,7 +57508,7 @@
         <v>3653</v>
       </c>
     </row>
-    <row r="660" spans="1:20" ht="225" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660">
         <v>4031</v>
       </c>
@@ -57567,7 +57567,7 @@
         <v>3659</v>
       </c>
     </row>
-    <row r="661" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661">
         <v>4032</v>
       </c>
@@ -57626,7 +57626,7 @@
         <v>3665</v>
       </c>
     </row>
-    <row r="662" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662">
         <v>4033</v>
       </c>
@@ -57685,7 +57685,7 @@
         <v>3670</v>
       </c>
     </row>
-    <row r="663" spans="1:20" ht="330" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663">
         <v>4034</v>
       </c>
@@ -57744,7 +57744,7 @@
         <v>3675</v>
       </c>
     </row>
-    <row r="664" spans="1:20" ht="210" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664">
         <v>4035</v>
       </c>
@@ -57803,7 +57803,7 @@
         <v>3680</v>
       </c>
     </row>
-    <row r="665" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665">
         <v>4036</v>
       </c>
@@ -57862,7 +57862,7 @@
         <v>3685</v>
       </c>
     </row>
-    <row r="666" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666">
         <v>4037</v>
       </c>
@@ -57921,7 +57921,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="667" spans="1:20" ht="285" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667">
         <v>4038</v>
       </c>
@@ -57980,7 +57980,7 @@
         <v>3695</v>
       </c>
     </row>
-    <row r="668" spans="1:20" ht="240" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668">
         <v>4039</v>
       </c>
@@ -58039,7 +58039,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="669" spans="1:20" ht="270" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669">
         <v>4040</v>
       </c>
@@ -58098,7 +58098,7 @@
         <v>3705</v>
       </c>
     </row>
-    <row r="670" spans="1:20" ht="255" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670">
         <v>4041</v>
       </c>
